--- a/devcom-rage-bait/data/rage-bait-data.xlsx
+++ b/devcom-rage-bait/data/rage-bait-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\Github-repository\data-consultation-2026\devcom-rage-bait\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\devcom-rage-bait\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9B5F45-C971-4BEF-B531-7BF2E0D3ECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872EA226-156F-48F0-AE5E-EE813B13B020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_data" sheetId="5" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8194" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8301" uniqueCount="380">
   <si>
     <t>Sex</t>
   </si>
@@ -1132,6 +1132,39 @@
   </si>
   <si>
     <t>I can easily recognize when a post is meant to provoke anger.</t>
+  </si>
+  <si>
+    <t>faculty</t>
+  </si>
+  <si>
+    <t>FME - Faculty of Management and Economics</t>
+  </si>
+  <si>
+    <t>FAFS - Faculty of Agriculture and Food Science</t>
+  </si>
+  <si>
+    <t>FNMS - Faculty of Natural and Mathematical Sciences</t>
+  </si>
+  <si>
+    <t>FoE - Faculty of Engineering</t>
+  </si>
+  <si>
+    <t>FTE - Faculty of Teacher Education</t>
+  </si>
+  <si>
+    <t>FAF - Faculty of Agriculture and Food Science</t>
+  </si>
+  <si>
+    <t>FFES - Faculty of Forestry and Environmental Sciences</t>
+  </si>
+  <si>
+    <t>FoN - Faculty of Nursing</t>
+  </si>
+  <si>
+    <t>FoC - Faculty of Computing</t>
+  </si>
+  <si>
+    <t>FVM - Faculty of Veterinary Medicine</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1256,7 +1289,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2127,9 +2159,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F748B0D-B97C-4C2F-9726-DF3017200DBC}">
   <dimension ref="A1:AJ102"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2239,7 +2271,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2349,7 +2381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2459,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2569,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2679,7 +2711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2789,7 +2821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2899,7 +2931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3009,7 +3041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3119,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3229,7 +3261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3339,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3449,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3559,7 +3591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3669,7 +3701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3779,7 +3811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3889,7 +3921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3999,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4109,7 +4141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4219,7 +4251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4329,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4439,7 +4471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4549,7 +4581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4659,7 +4691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4769,7 +4801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4879,7 +4911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4989,7 +5021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5099,7 +5131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5209,7 +5241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5319,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5429,7 +5461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5539,7 +5571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5649,7 +5681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5759,7 +5791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5869,7 +5901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5979,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6089,7 +6121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6199,7 +6231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6309,7 +6341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6419,7 +6451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6529,7 +6561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6639,7 +6671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6749,7 +6781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6859,7 +6891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6969,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7079,7 +7111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7189,7 +7221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7299,7 +7331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7409,7 +7441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7519,7 +7551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7629,7 +7661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7739,7 +7771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7849,7 +7881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7959,7 +7991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8069,7 +8101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8179,7 +8211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8289,7 +8321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8399,7 +8431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8509,7 +8541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8619,7 +8651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8729,7 +8761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8839,7 +8871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8949,7 +8981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9059,7 +9091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9169,7 +9201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9279,7 +9311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9389,7 +9421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9499,7 +9531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9609,7 +9641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9719,7 +9751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9829,7 +9861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9939,7 +9971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -10049,7 +10081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -10159,7 +10191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10269,7 +10301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10379,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10489,7 +10521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10599,7 +10631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10709,7 +10741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10819,7 +10851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10929,7 +10961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -11039,7 +11071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -11149,7 +11181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11259,7 +11291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11369,7 +11401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11479,7 +11511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11589,7 +11621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11699,7 +11731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11809,7 +11841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11919,7 +11951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -12029,7 +12061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12139,7 +12171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12249,7 +12281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12359,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12469,7 +12501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12579,7 +12611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12689,7 +12721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12799,7 +12831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12909,7 +12941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -13019,7 +13051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -13129,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -13239,7 +13271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13356,13 +13388,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E2DA7B-3D93-4C4B-BEA2-8DBD8745B760}">
-  <dimension ref="A1:E107"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="5" width="68.6640625" customWidth="1"/>
+    <col min="2" max="6" width="68.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13370,16 +13402,19 @@
         <v>255</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -13387,16 +13422,19 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>53</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -13404,16 +13442,19 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>57</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -13421,16 +13462,19 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>60</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -13438,16 +13482,19 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -13455,16 +13502,19 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>66</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -13472,16 +13522,19 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -13489,16 +13542,19 @@
         <v>71</v>
       </c>
       <c r="C8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>73</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -13506,16 +13562,19 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>75</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -13523,16 +13582,19 @@
         <v>76</v>
       </c>
       <c r="C10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>77</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -13540,16 +13602,19 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -13557,16 +13622,19 @@
         <v>81</v>
       </c>
       <c r="C12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D12" t="s">
         <v>82</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>83</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -13574,16 +13642,19 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>85</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -13591,16 +13662,19 @@
         <v>86</v>
       </c>
       <c r="C14" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>87</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -13608,16 +13682,19 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
+        <v>373</v>
+      </c>
+      <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>89</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -13625,16 +13702,19 @@
         <v>90</v>
       </c>
       <c r="C16" t="s">
+        <v>371</v>
+      </c>
+      <c r="D16" t="s">
         <v>91</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>80</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -13642,16 +13722,19 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
+        <v>373</v>
+      </c>
+      <c r="D17" t="s">
         <v>93</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>68</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -13659,16 +13742,19 @@
         <v>94</v>
       </c>
       <c r="C18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>87</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -13676,16 +13762,19 @@
         <v>95</v>
       </c>
       <c r="C19" t="s">
+        <v>371</v>
+      </c>
+      <c r="D19" t="s">
         <v>96</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>97</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -13693,16 +13782,19 @@
         <v>98</v>
       </c>
       <c r="C20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D20" t="s">
         <v>99</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>100</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -13710,16 +13802,19 @@
         <v>101</v>
       </c>
       <c r="C21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>102</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -13727,16 +13822,19 @@
         <v>104</v>
       </c>
       <c r="C22" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22" t="s">
         <v>91</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>105</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -13744,16 +13842,19 @@
         <v>106</v>
       </c>
       <c r="C23" t="s">
+        <v>371</v>
+      </c>
+      <c r="D23" t="s">
         <v>107</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>108</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -13761,16 +13862,19 @@
         <v>109</v>
       </c>
       <c r="C24" t="s">
+        <v>371</v>
+      </c>
+      <c r="D24" t="s">
         <v>110</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>111</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -13778,16 +13882,19 @@
         <v>112</v>
       </c>
       <c r="C25" t="s">
+        <v>374</v>
+      </c>
+      <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>89</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -13795,16 +13902,19 @@
         <v>114</v>
       </c>
       <c r="C26" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" t="s">
         <v>115</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>116</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -13812,16 +13922,19 @@
         <v>117</v>
       </c>
       <c r="C27" t="s">
+        <v>371</v>
+      </c>
+      <c r="D27" t="s">
         <v>118</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>119</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -13829,16 +13942,19 @@
         <v>120</v>
       </c>
       <c r="C28" t="s">
+        <v>370</v>
+      </c>
+      <c r="D28" t="s">
         <v>121</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>122</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -13846,16 +13962,19 @@
         <v>123</v>
       </c>
       <c r="C29" t="s">
+        <v>372</v>
+      </c>
+      <c r="D29" t="s">
         <v>93</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>124</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -13863,16 +13982,19 @@
         <v>92</v>
       </c>
       <c r="C30" t="s">
+        <v>373</v>
+      </c>
+      <c r="D30" t="s">
         <v>52</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>125</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -13880,16 +14002,19 @@
         <v>126</v>
       </c>
       <c r="C31" t="s">
+        <v>370</v>
+      </c>
+      <c r="D31" t="s">
         <v>56</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>89</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -13897,16 +14022,19 @@
         <v>127</v>
       </c>
       <c r="C32" t="s">
+        <v>377</v>
+      </c>
+      <c r="D32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>128</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -13914,16 +14042,19 @@
         <v>129</v>
       </c>
       <c r="C33" t="s">
+        <v>371</v>
+      </c>
+      <c r="D33" t="s">
         <v>118</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>130</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -13931,16 +14062,19 @@
         <v>131</v>
       </c>
       <c r="C34" t="s">
+        <v>371</v>
+      </c>
+      <c r="D34" t="s">
         <v>72</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>132</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -13948,16 +14082,19 @@
         <v>133</v>
       </c>
       <c r="C35" t="s">
+        <v>377</v>
+      </c>
+      <c r="D35" t="s">
         <v>134</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>135</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -13965,16 +14102,19 @@
         <v>136</v>
       </c>
       <c r="C36" t="s">
+        <v>377</v>
+      </c>
+      <c r="D36" t="s">
         <v>137</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>138</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -13982,16 +14122,19 @@
         <v>139</v>
       </c>
       <c r="C37" t="s">
+        <v>372</v>
+      </c>
+      <c r="D37" t="s">
         <v>52</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>140</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -13999,16 +14142,19 @@
         <v>141</v>
       </c>
       <c r="C38" t="s">
+        <v>370</v>
+      </c>
+      <c r="D38" t="s">
         <v>52</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>142</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -14016,16 +14162,19 @@
         <v>106</v>
       </c>
       <c r="C39" t="s">
+        <v>371</v>
+      </c>
+      <c r="D39" t="s">
         <v>143</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>125</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -14033,16 +14182,19 @@
         <v>144</v>
       </c>
       <c r="C40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D40" t="s">
         <v>145</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>146</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -14050,16 +14202,19 @@
         <v>147</v>
       </c>
       <c r="C41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D41" t="s">
         <v>52</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>148</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -14067,16 +14222,19 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
+        <v>372</v>
+      </c>
+      <c r="D42" t="s">
         <v>149</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>87</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -14084,16 +14242,19 @@
         <v>150</v>
       </c>
       <c r="C43" t="s">
+        <v>373</v>
+      </c>
+      <c r="D43" t="s">
         <v>72</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>151</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>70</v>
       </c>
@@ -14101,16 +14262,19 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D44" t="s">
         <v>118</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>128</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>70</v>
       </c>
@@ -14118,16 +14282,19 @@
         <v>153</v>
       </c>
       <c r="C45" t="s">
+        <v>371</v>
+      </c>
+      <c r="D45" t="s">
         <v>52</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>116</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -14135,16 +14302,19 @@
         <v>90</v>
       </c>
       <c r="C46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46" t="s">
         <v>52</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>154</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -14152,16 +14322,19 @@
         <v>155</v>
       </c>
       <c r="C47" t="s">
+        <v>371</v>
+      </c>
+      <c r="D47" t="s">
         <v>156</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>157</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -14169,16 +14342,19 @@
         <v>158</v>
       </c>
       <c r="C48" t="s">
+        <v>371</v>
+      </c>
+      <c r="D48" t="s">
         <v>56</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>148</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>70</v>
       </c>
@@ -14186,16 +14362,19 @@
         <v>159</v>
       </c>
       <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49" t="s">
         <v>160</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>161</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -14203,16 +14382,19 @@
         <v>162</v>
       </c>
       <c r="C50" t="s">
+        <v>371</v>
+      </c>
+      <c r="D50" t="s">
         <v>163</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>164</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -14220,16 +14402,19 @@
         <v>95</v>
       </c>
       <c r="C51" t="s">
+        <v>371</v>
+      </c>
+      <c r="D51" t="s">
         <v>56</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>68</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>70</v>
       </c>
@@ -14237,16 +14422,19 @@
         <v>165</v>
       </c>
       <c r="C52" t="s">
+        <v>371</v>
+      </c>
+      <c r="D52" t="s">
         <v>166</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>167</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -14254,16 +14442,19 @@
         <v>131</v>
       </c>
       <c r="C53" t="s">
+        <v>371</v>
+      </c>
+      <c r="D53" t="s">
         <v>52</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>148</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -14271,16 +14462,19 @@
         <v>168</v>
       </c>
       <c r="C54" t="s">
+        <v>371</v>
+      </c>
+      <c r="D54" t="s">
         <v>163</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>169</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -14288,16 +14482,19 @@
         <v>131</v>
       </c>
       <c r="C55" t="s">
+        <v>371</v>
+      </c>
+      <c r="D55" t="s">
         <v>52</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>170</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>50</v>
       </c>
@@ -14305,16 +14502,19 @@
         <v>171</v>
       </c>
       <c r="C56" t="s">
+        <v>373</v>
+      </c>
+      <c r="D56" t="s">
         <v>52</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>172</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -14322,16 +14522,19 @@
         <v>173</v>
       </c>
       <c r="C57" t="s">
+        <v>374</v>
+      </c>
+      <c r="D57" t="s">
         <v>52</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>148</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -14339,16 +14542,19 @@
         <v>174</v>
       </c>
       <c r="C58" t="s">
+        <v>377</v>
+      </c>
+      <c r="D58" t="s">
         <v>160</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>175</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -14356,16 +14562,19 @@
         <v>176</v>
       </c>
       <c r="C59" t="s">
+        <v>371</v>
+      </c>
+      <c r="D59" t="s">
         <v>177</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>178</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -14373,16 +14582,19 @@
         <v>179</v>
       </c>
       <c r="C60" t="s">
+        <v>371</v>
+      </c>
+      <c r="D60" t="s">
         <v>52</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>180</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -14390,16 +14602,19 @@
         <v>182</v>
       </c>
       <c r="C61" t="s">
+        <v>374</v>
+      </c>
+      <c r="D61" t="s">
         <v>183</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>175</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -14407,16 +14622,19 @@
         <v>184</v>
       </c>
       <c r="C62" t="s">
+        <v>371</v>
+      </c>
+      <c r="D62" t="s">
         <v>185</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>89</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -14424,16 +14642,19 @@
         <v>186</v>
       </c>
       <c r="C63" t="s">
+        <v>370</v>
+      </c>
+      <c r="D63" t="s">
         <v>187</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>188</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -14441,16 +14662,19 @@
         <v>189</v>
       </c>
       <c r="C64" t="s">
+        <v>371</v>
+      </c>
+      <c r="D64" t="s">
         <v>163</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>190</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -14458,16 +14682,19 @@
         <v>191</v>
       </c>
       <c r="C65" t="s">
+        <v>370</v>
+      </c>
+      <c r="D65" t="s">
         <v>187</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>192</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -14475,16 +14702,19 @@
         <v>193</v>
       </c>
       <c r="C66" t="s">
+        <v>378</v>
+      </c>
+      <c r="D66" t="s">
         <v>194</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>195</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>50</v>
       </c>
@@ -14492,16 +14722,19 @@
         <v>196</v>
       </c>
       <c r="C67" t="s">
+        <v>371</v>
+      </c>
+      <c r="D67" t="s">
         <v>52</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>105</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>50</v>
       </c>
@@ -14509,16 +14742,19 @@
         <v>197</v>
       </c>
       <c r="C68" t="s">
+        <v>370</v>
+      </c>
+      <c r="D68" t="s">
         <v>52</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>188</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>50</v>
       </c>
@@ -14526,16 +14762,19 @@
         <v>198</v>
       </c>
       <c r="C69" t="s">
+        <v>378</v>
+      </c>
+      <c r="D69" t="s">
         <v>199</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>200</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -14543,16 +14782,19 @@
         <v>201</v>
       </c>
       <c r="C70" t="s">
+        <v>378</v>
+      </c>
+      <c r="D70" t="s">
         <v>72</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>202</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -14560,16 +14802,19 @@
         <v>203</v>
       </c>
       <c r="C71" t="s">
+        <v>370</v>
+      </c>
+      <c r="D71" t="s">
         <v>204</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>205</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>50</v>
       </c>
@@ -14577,16 +14822,19 @@
         <v>51</v>
       </c>
       <c r="C72" t="s">
+        <v>370</v>
+      </c>
+      <c r="D72" t="s">
         <v>206</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>167</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>50</v>
       </c>
@@ -14594,16 +14842,19 @@
         <v>207</v>
       </c>
       <c r="C73" t="s">
+        <v>374</v>
+      </c>
+      <c r="D73" t="s">
         <v>56</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>89</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>50</v>
       </c>
@@ -14611,16 +14862,19 @@
         <v>208</v>
       </c>
       <c r="C74" t="s">
+        <v>371</v>
+      </c>
+      <c r="D74" t="s">
         <v>72</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>89</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>70</v>
       </c>
@@ -14628,16 +14882,19 @@
         <v>209</v>
       </c>
       <c r="C75" t="s">
+        <v>371</v>
+      </c>
+      <c r="D75" t="s">
         <v>56</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>205</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>50</v>
       </c>
@@ -14645,16 +14902,19 @@
         <v>210</v>
       </c>
       <c r="C76" t="s">
+        <v>371</v>
+      </c>
+      <c r="D76" t="s">
         <v>211</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>212</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>50</v>
       </c>
@@ -14662,16 +14922,19 @@
         <v>213</v>
       </c>
       <c r="C77" t="s">
+        <v>374</v>
+      </c>
+      <c r="D77" t="s">
         <v>56</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>212</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>50</v>
       </c>
@@ -14679,16 +14942,19 @@
         <v>214</v>
       </c>
       <c r="C78" t="s">
+        <v>374</v>
+      </c>
+      <c r="D78" t="s">
         <v>187</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>212</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -14696,16 +14962,19 @@
         <v>215</v>
       </c>
       <c r="C79" t="s">
+        <v>374</v>
+      </c>
+      <c r="D79" t="s">
         <v>199</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>89</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>50</v>
       </c>
@@ -14713,16 +14982,19 @@
         <v>216</v>
       </c>
       <c r="C80" t="s">
+        <v>374</v>
+      </c>
+      <c r="D80" t="s">
         <v>118</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>217</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>50</v>
       </c>
@@ -14730,16 +15002,19 @@
         <v>218</v>
       </c>
       <c r="C81" t="s">
+        <v>374</v>
+      </c>
+      <c r="D81" t="s">
         <v>82</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>219</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -14747,16 +15022,19 @@
         <v>216</v>
       </c>
       <c r="C82" t="s">
+        <v>374</v>
+      </c>
+      <c r="D82" t="s">
         <v>56</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>220</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>70</v>
       </c>
@@ -14764,16 +15042,19 @@
         <v>221</v>
       </c>
       <c r="C83" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" t="s">
         <v>222</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>223</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>50</v>
       </c>
@@ -14781,16 +15062,19 @@
         <v>214</v>
       </c>
       <c r="C84" t="s">
+        <v>374</v>
+      </c>
+      <c r="D84" t="s">
         <v>56</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>205</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>50</v>
       </c>
@@ -14798,16 +15082,19 @@
         <v>214</v>
       </c>
       <c r="C85" t="s">
+        <v>374</v>
+      </c>
+      <c r="D85" t="s">
         <v>52</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>212</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>50</v>
       </c>
@@ -14815,16 +15102,19 @@
         <v>224</v>
       </c>
       <c r="C86" t="s">
+        <v>374</v>
+      </c>
+      <c r="D86" t="s">
         <v>222</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>225</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>50</v>
       </c>
@@ -14832,16 +15122,19 @@
         <v>226</v>
       </c>
       <c r="C87" t="s">
+        <v>374</v>
+      </c>
+      <c r="D87" t="s">
         <v>91</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>119</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>50</v>
       </c>
@@ -14849,16 +15142,19 @@
         <v>227</v>
       </c>
       <c r="C88" t="s">
+        <v>374</v>
+      </c>
+      <c r="D88" t="s">
         <v>187</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>228</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>50</v>
       </c>
@@ -14866,16 +15162,19 @@
         <v>229</v>
       </c>
       <c r="C89" t="s">
+        <v>374</v>
+      </c>
+      <c r="D89" t="s">
         <v>56</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>230</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>50</v>
       </c>
@@ -14883,16 +15182,19 @@
         <v>231</v>
       </c>
       <c r="C90" t="s">
+        <v>374</v>
+      </c>
+      <c r="D90" t="s">
         <v>56</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>142</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>50</v>
       </c>
@@ -14900,16 +15202,19 @@
         <v>232</v>
       </c>
       <c r="C91" t="s">
+        <v>374</v>
+      </c>
+      <c r="D91" t="s">
         <v>59</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>233</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>50</v>
       </c>
@@ -14917,16 +15222,19 @@
         <v>234</v>
       </c>
       <c r="C92" t="s">
+        <v>374</v>
+      </c>
+      <c r="D92" t="s">
         <v>56</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>116</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>50</v>
       </c>
@@ -14934,16 +15242,19 @@
         <v>235</v>
       </c>
       <c r="C93" t="s">
+        <v>374</v>
+      </c>
+      <c r="D93" t="s">
         <v>59</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>89</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>50</v>
       </c>
@@ -14951,16 +15262,19 @@
         <v>236</v>
       </c>
       <c r="C94" t="s">
+        <v>379</v>
+      </c>
+      <c r="D94" t="s">
         <v>237</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>151</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>50</v>
       </c>
@@ -14968,16 +15282,19 @@
         <v>155</v>
       </c>
       <c r="C95" t="s">
+        <v>371</v>
+      </c>
+      <c r="D95" t="s">
         <v>238</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>239</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>50</v>
       </c>
@@ -14985,16 +15302,19 @@
         <v>90</v>
       </c>
       <c r="C96" t="s">
+        <v>371</v>
+      </c>
+      <c r="D96" t="s">
         <v>52</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>240</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>70</v>
       </c>
@@ -15002,16 +15322,19 @@
         <v>90</v>
       </c>
       <c r="C97" t="s">
+        <v>371</v>
+      </c>
+      <c r="D97" t="s">
         <v>72</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>241</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>70</v>
       </c>
@@ -15019,16 +15342,19 @@
         <v>242</v>
       </c>
       <c r="C98" t="s">
+        <v>371</v>
+      </c>
+      <c r="D98" t="s">
         <v>113</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>169</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>70</v>
       </c>
@@ -15036,16 +15362,19 @@
         <v>243</v>
       </c>
       <c r="C99" t="s">
+        <v>370</v>
+      </c>
+      <c r="D99" t="s">
         <v>52</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>169</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>50</v>
       </c>
@@ -15053,16 +15382,19 @@
         <v>244</v>
       </c>
       <c r="C100" t="s">
+        <v>372</v>
+      </c>
+      <c r="D100" t="s">
         <v>113</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>148</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>70</v>
       </c>
@@ -15070,16 +15402,19 @@
         <v>243</v>
       </c>
       <c r="C101" t="s">
+        <v>370</v>
+      </c>
+      <c r="D101" t="s">
         <v>121</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>167</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>50</v>
       </c>
@@ -15087,16 +15422,19 @@
         <v>243</v>
       </c>
       <c r="C102" t="s">
+        <v>370</v>
+      </c>
+      <c r="D102" t="s">
         <v>52</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>125</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>50</v>
       </c>
@@ -15104,16 +15442,19 @@
         <v>245</v>
       </c>
       <c r="C103" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" t="s">
         <v>246</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>87</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>50</v>
       </c>
@@ -15121,16 +15462,19 @@
         <v>247</v>
       </c>
       <c r="C104" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" t="s">
         <v>91</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>190</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>50</v>
       </c>
@@ -15138,16 +15482,19 @@
         <v>248</v>
       </c>
       <c r="C105" t="s">
+        <v>371</v>
+      </c>
+      <c r="D105" t="s">
         <v>52</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>169</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -15155,16 +15502,19 @@
         <v>214</v>
       </c>
       <c r="C106" t="s">
+        <v>374</v>
+      </c>
+      <c r="D106" t="s">
         <v>187</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>249</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>50</v>
       </c>
@@ -15172,12 +15522,15 @@
         <v>131</v>
       </c>
       <c r="C107" t="s">
+        <v>371</v>
+      </c>
+      <c r="D107" t="s">
         <v>222</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>250</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15189,396 +15542,396 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B7F026-A08E-42A2-A8B1-22AB0CB70994}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="42.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="42.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>261</v>
       </c>
       <c r="B1" t="s">
         <v>259</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>43</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>262</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>262</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>262</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>262</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>46</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>46</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>47</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>47</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>49</v>
       </c>
       <c r="B34" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>49</v>
       </c>
       <c r="B35" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" t="s">
         <v>360</v>
       </c>
     </row>
@@ -15590,9 +15943,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA5DABD0-CE2C-4CF2-BA12-99A784FBD4F6}">
   <dimension ref="E2:BX2"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="5:76" x14ac:dyDescent="0.25">
+    <row r="2" spans="5:76" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
         <v>263</v>
       </c>
@@ -15821,18 +16174,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AJ103"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="36" width="21.33203125" customWidth="1"/>
-    <col min="37" max="42" width="37.6640625" customWidth="1"/>
-    <col min="43" max="43" width="30.44140625" customWidth="1"/>
-    <col min="44" max="49" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="36" width="21.28515625" customWidth="1"/>
+    <col min="37" max="42" width="37.7109375" customWidth="1"/>
+    <col min="43" max="43" width="30.42578125" customWidth="1"/>
+    <col min="44" max="49" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
@@ -15882,7 +16235,7 @@
       <c r="AI1" s="13"/>
       <c r="AJ1" s="13"/>
     </row>
-    <row r="2" spans="1:36" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -15992,7 +16345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -16102,7 +16455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -16212,7 +16565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -16322,7 +16675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -16432,7 +16785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -16542,7 +16895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -16652,7 +17005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -16762,7 +17115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -16872,7 +17225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -16982,7 +17335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -17092,7 +17445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -17202,7 +17555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -17312,7 +17665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -17422,7 +17775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -17532,7 +17885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -17642,7 +17995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -17752,7 +18105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -17862,7 +18215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -17972,7 +18325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -18082,7 +18435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -18192,7 +18545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -18302,7 +18655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -18412,7 +18765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -18522,7 +18875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -18632,7 +18985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -18742,7 +19095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -18852,7 +19205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -18962,7 +19315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -19072,7 +19425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -19182,7 +19535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -19292,7 +19645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -19402,7 +19755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -19512,7 +19865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -19622,7 +19975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -19732,7 +20085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -19842,7 +20195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -19952,7 +20305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -20062,7 +20415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -20172,7 +20525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -20282,7 +20635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -20392,7 +20745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -20502,7 +20855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -20612,7 +20965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -20722,7 +21075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -20832,7 +21185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -20942,7 +21295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -21052,7 +21405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -21162,7 +21515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -21272,7 +21625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -21382,7 +21735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -21492,7 +21845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -21602,7 +21955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -21712,7 +22065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -21822,7 +22175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -21932,7 +22285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -22042,7 +22395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -22152,7 +22505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -22262,7 +22615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -22372,7 +22725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -22482,7 +22835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -22592,7 +22945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -22702,7 +23055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -22812,7 +23165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -22922,7 +23275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -23032,7 +23385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -23142,7 +23495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -23252,7 +23605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -23362,7 +23715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -23472,7 +23825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -23582,7 +23935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -23692,7 +24045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -23802,7 +24155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -23912,7 +24265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -24022,7 +24375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -24132,7 +24485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -24242,7 +24595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -24352,7 +24705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -24462,7 +24815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -24572,7 +24925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -24682,7 +25035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -24792,7 +25145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -24902,7 +25255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -25012,7 +25365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -25122,7 +25475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -25232,7 +25585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -25342,7 +25695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -25452,7 +25805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -25562,7 +25915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -25672,7 +26025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -25782,7 +26135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -25892,7 +26245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -26002,7 +26355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -26112,7 +26465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -26222,7 +26575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -26332,7 +26685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -26442,7 +26795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -26552,7 +26905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -26662,7 +27015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -26772,7 +27125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -26882,7 +27235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -26992,7 +27345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -27123,12 +27476,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9697C6DC-13D6-49C2-A097-28C4ABA82B15}">
   <dimension ref="A1:F107"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="6" width="36.5546875" customWidth="1"/>
+    <col min="2" max="6" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -27145,7 +27498,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -27165,7 +27518,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -27185,7 +27538,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -27205,7 +27558,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -27225,7 +27578,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -27245,7 +27598,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -27265,7 +27618,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -27285,7 +27638,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -27305,7 +27658,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -27325,7 +27678,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -27345,7 +27698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -27365,7 +27718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -27385,7 +27738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -27405,7 +27758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -27425,7 +27778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -27445,7 +27798,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -27465,7 +27818,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -27485,7 +27838,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -27505,7 +27858,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -27525,7 +27878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -27545,7 +27898,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -27565,7 +27918,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -27585,7 +27938,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -27605,7 +27958,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -27625,7 +27978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -27645,7 +27998,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -27665,7 +28018,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -27685,7 +28038,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -27705,7 +28058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -27725,7 +28078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -27745,7 +28098,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -27765,7 +28118,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -27785,7 +28138,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -27805,7 +28158,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -27825,7 +28178,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -27845,7 +28198,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -27865,7 +28218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -27885,7 +28238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -27905,7 +28258,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -27925,7 +28278,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -27945,7 +28298,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -27965,7 +28318,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -27985,7 +28338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -28005,7 +28358,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -28025,7 +28378,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -28045,7 +28398,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -28065,7 +28418,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -28085,7 +28438,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -28105,7 +28458,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -28125,7 +28478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -28145,7 +28498,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -28165,7 +28518,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -28185,7 +28538,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -28205,7 +28558,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -28225,7 +28578,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -28245,7 +28598,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -28265,7 +28618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -28285,7 +28638,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -28305,7 +28658,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -28325,7 +28678,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -28345,7 +28698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -28365,7 +28718,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -28385,7 +28738,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -28405,7 +28758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -28425,7 +28778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -28445,7 +28798,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -28465,7 +28818,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -28485,7 +28838,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -28505,7 +28858,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -28525,7 +28878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -28545,7 +28898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -28565,7 +28918,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -28585,7 +28938,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -28605,7 +28958,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -28625,7 +28978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -28645,7 +28998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -28665,7 +29018,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -28685,7 +29038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -28705,7 +29058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -28725,7 +29078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -28745,7 +29098,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -28765,7 +29118,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -28785,7 +29138,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -28805,7 +29158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -28825,7 +29178,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -28845,7 +29198,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -28865,7 +29218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -28885,7 +29238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -28905,7 +29258,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -28925,7 +29278,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -28945,7 +29298,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -28965,7 +29318,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -28985,7 +29338,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -29005,7 +29358,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -29025,7 +29378,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -29045,7 +29398,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -29065,7 +29418,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -29085,7 +29438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -29105,7 +29458,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -29125,7 +29478,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -29145,7 +29498,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -29165,7 +29518,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -29185,7 +29538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -29205,7 +29558,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -29225,7 +29578,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -29245,7 +29598,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
